--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 04/09/2026 16:42 UTC</t>
+          <t>Generado: 07/09/2026 18:04 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-04T16:42:54+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-07T18:04:55+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 07/09/2026 18:04 UTC</t>
+          <t>Generado: 08/09/2026 17:03 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-07T18:04:55+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-08T17:03:10+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 08/09/2026 17:03 UTC</t>
+          <t>Generado: 09/09/2026 17:01 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-08T17:03:10+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-09T17:01:06+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 09/09/2026 17:01 UTC</t>
+          <t>Generado: 10/09/2026 16:52 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-09T17:01:06+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-10T16:52:58+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 10/09/2026 16:52 UTC</t>
+          <t>Generado: 11/09/2026 16:53 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-10T16:52:58+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-11T16:53:32+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 11/09/2026 16:53 UTC</t>
+          <t>Generado: 14/09/2026 18:19 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-11T16:53:32+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-14T18:19:53+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 14/09/2026 18:19 UTC</t>
+          <t>Generado: 15/09/2026 17:27 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-14T18:19:53+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-15T17:27:31+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 15/09/2026 17:27 UTC</t>
+          <t>Generado: 16/09/2026 17:26 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-15T17:27:31+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-16T17:26:50+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 16/09/2026 17:26 UTC</t>
+          <t>Generado: 17/09/2026 17:26 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-16T17:26:50+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-17T17:26:56+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 17/09/2026 17:26 UTC</t>
+          <t>Generado: 18/09/2026 16:55 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-17T17:26:56+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-18T16:55:16+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 18/09/2026 16:55 UTC</t>
+          <t>Generado: 21/09/2026 18:27 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-18T16:55:16+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-21T18:27:03+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 21/09/2026 18:27 UTC</t>
+          <t>Generado: 22/09/2026 17:30 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-21T18:27:03+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-22T17:30:44+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 22/09/2026 17:30 UTC</t>
+          <t>Generado: 23/09/2026 17:41 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-22T17:30:44+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-23T17:41:32+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 23/09/2026 17:41 UTC</t>
+          <t>Generado: 24/09/2026 17:43 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-23T17:41:32+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-24T17:43:33+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 24/09/2026 17:43 UTC</t>
+          <t>Generado: 25/09/2026 17:45 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-24T17:43:33+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-25T17:45:04+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 25/09/2026 17:45 UTC</t>
+          <t>Generado: 28/09/2026 19:58 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-25T17:45:04+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-28T19:58:36+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 28/09/2026 19:58 UTC</t>
+          <t>Generado: 29/09/2026 18:26 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-28T19:58:36+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-29T18:26:46+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 29/09/2026 18:26 UTC</t>
+          <t>Generado: 30/09/2026 18:15 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-29T18:26:46+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-09-30T18:15:35+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 30/09/2026 18:15 UTC</t>
+          <t>Generado: 01/10/2026 18:40 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-09-30T18:15:35+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-01T18:40:51+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 01/10/2026 18:40 UTC</t>
+          <t>Generado: 02/10/2026 18:11 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-01T18:40:51+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-02T18:11:36+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 02/10/2026 18:11 UTC</t>
+          <t>Generado: 05/10/2026 21:01 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-02T18:11:36+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-05T21:01:40+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 05/10/2026 21:01 UTC</t>
+          <t>Generado: 06/10/2026 18:45 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-05T21:01:40+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-06T18:45:57+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 06/10/2026 18:45 UTC</t>
+          <t>Generado: 07/10/2026 19:11 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-06T18:45:57+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-07T19:11:31+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 07/10/2026 19:11 UTC</t>
+          <t>Generado: 08/10/2026 19:07 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-07T19:11:31+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-08T19:07:52+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 08/10/2026 19:07 UTC</t>
+          <t>Generado: 09/10/2026 18:38 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-08T19:07:52+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-09T18:38:51+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 09/10/2026 18:38 UTC</t>
+          <t>Generado: 12/10/2026 21:32 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-09T18:38:51+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-12T21:32:20+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 12/10/2026 21:32 UTC</t>
+          <t>Generado: 13/10/2026 19:43 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-12T21:32:20+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-13T19:43:39+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 13/10/2026 19:43 UTC</t>
+          <t>Generado: 14/10/2026 17:45 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-13T19:43:39+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-14T17:45:46+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 14/10/2026 17:45 UTC</t>
+          <t>Generado: 15/10/2026 17:34 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-14T17:45:46+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-15T17:34:52+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 15/10/2026 17:34 UTC</t>
+          <t>Generado: 16/10/2026 17:09 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-15T17:34:52+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-16T17:09:21+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 16/10/2026 17:09 UTC</t>
+          <t>Generado: 19/10/2026 18:58 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-16T17:09:21+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-19T18:58:26+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 19/10/2026 18:58 UTC</t>
+          <t>Generado: 20/10/2026 17:45 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-19T18:58:26+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-20T17:45:25+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 20/10/2026 17:45 UTC</t>
+          <t>Generado: 21/10/2026 17:53 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-20T17:45:25+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-21T17:53:13+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 21/10/2026 17:53 UTC</t>
+          <t>Generado: 22/10/2026 17:50 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-21T17:53:13+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-22T17:50:41+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 22/10/2026 17:50 UTC</t>
+          <t>Generado: 23/10/2026 17:40 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-22T17:50:41+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-23T17:40:38+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 23/10/2026 17:40 UTC</t>
+          <t>Generado: 26/10/2026 19:00 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-23T17:40:38+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-26T19:00:30+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 26/10/2026 19:00 UTC</t>
+          <t>Generado: 27/10/2026 18:32 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-26T19:00:30+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-27T18:32:00+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 27/10/2026 18:32 UTC</t>
+          <t>Generado: 28/10/2026 18:38 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-27T18:32:00+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-28T18:38:33+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 28/10/2026 18:38 UTC</t>
+          <t>Generado: 29/10/2026 18:46 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-28T18:38:33+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-29T18:46:09+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 29/10/2026 18:46 UTC</t>
+          <t>Generado: 30/10/2026 18:24 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-10-29T18:46:09+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-10-30T18:24:26+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
